--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260626.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>7,550,000</t>
+          <t>1,950,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,950,000</t>
+          <t>7,550,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
